--- a/examples/Config/Excel/Server/SceneConfig.xlsx
+++ b/examples/Config/Excel/Server/SceneConfig.xlsx
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -519,7 +519,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -542,13 +542,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -708,6 +701,20 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -717,29 +724,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -756,8 +743,14 @@
       <name val="Microsoft Tai Le"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -821,12 +814,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1108,148 +1095,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1272,16 +1259,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1812,7 +1799,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.1666666666667" customWidth="1"/>
@@ -2166,6 +2153,11 @@
       </c>
       <c r="L11" s="4" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/examples/Config/Excel/Server/SceneConfig.xlsx
+++ b/examples/Config/Excel/Server/SceneConfig.xlsx
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -467,7 +467,7 @@
     <t>Gate</t>
   </si>
   <si>
-    <t>KCP</t>
+    <t>TCP</t>
   </si>
   <si>
     <t>Gate中心</t>
@@ -1856,16 +1856,36 @@
       <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
+      <c r="C2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.25" spans="2:12">
       <c r="B3" s="7" t="s">

--- a/examples/Config/Excel/Server/SceneConfig.xlsx
+++ b/examples/Config/Excel/Server/SceneConfig.xlsx
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="48">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1531,6 +1531,153 @@
           <a:spAutoFit/>
         </a:bodyPr>
         <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>736599</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="文本框 2"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8978265" y="4062730"/>
+          <a:ext cx="635" cy="172085"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
         <a:p>
           <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
         </a:p>
@@ -2041,7 +2188,7 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="15.4" spans="2:12">
       <c r="B8" s="10">
-        <f>B7+1</f>
+        <f t="shared" ref="B8:B12" si="0">B7+1</f>
         <v>2</v>
       </c>
       <c r="C8" s="4">
@@ -2078,7 +2225,7 @@
     </row>
     <row r="9" s="1" customFormat="1" ht="15.4" spans="2:12">
       <c r="B9" s="10">
-        <f>B8+1</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C9" s="4">
@@ -2111,7 +2258,7 @@
     </row>
     <row r="10" s="1" customFormat="1" ht="15.4" spans="2:12">
       <c r="B10" s="10">
-        <f>B9+1</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C10" s="4">
@@ -2144,7 +2291,7 @@
     </row>
     <row r="11" s="1" customFormat="1" ht="15.4" spans="2:12">
       <c r="B11" s="10">
-        <f>B10+1</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C11" s="4">
@@ -2175,6 +2322,43 @@
         <v>37</v>
       </c>
     </row>
+    <row r="12" s="1" customFormat="1" ht="15.4" spans="2:12">
+      <c r="B12" s="10">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1006</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="4">
+        <v>20001</v>
+      </c>
+      <c r="J12" s="4">
+        <v>11007</v>
+      </c>
+      <c r="K12" s="4">
+        <f>INDEX(SceneTypeConfig!$A$3:$A$90000,MATCH(G12,SceneTypeConfig!$B$3:$B$90000,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="15" spans="3:3">
       <c r="C15" t="s">
         <v>0</v>
@@ -2182,13 +2366,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F7:F11">
       <formula1>"MainThread,MultiThread,ThreadPool"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G12 G7:G11">
       <formula1>SceneTypeConfig!$B$3:$B$1048576</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7:H11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12 H7:H11">
       <formula1>"None,KCP,TCP,WebSocket,HTTP"</formula1>
     </dataValidation>
   </dataValidations>

--- a/examples/Config/Excel/Server/SceneConfig.xlsx
+++ b/examples/Config/Excel/Server/SceneConfig.xlsx
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="48">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1946,7 +1946,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.1666666666667" customWidth="1"/>
@@ -2357,11 +2357,6 @@
       </c>
       <c r="L12" s="4" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="3:3">
-      <c r="C15" t="s">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
